--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487929_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487929_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2808</v>
+        <v>6.6652</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0536</v>
+        <v>4.2913</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2272</v>
+        <v>2.374</v>
       </c>
       <c r="G2" t="n">
         <v>3.1363</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5389</v>
+        <v>0.9233</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2948</v>
+        <v>0.5325</v>
       </c>
       <c r="U2" t="n">
-        <v>0.244</v>
+        <v>0.3908</v>
       </c>
       <c r="V2" t="n">
         <v>1.9813</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8532</v>
+        <v>4.7806</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4009</v>
+        <v>3.7394</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4522</v>
+        <v>1.0412</v>
       </c>
       <c r="G3" t="n">
         <v>5.4058</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1986</v>
+        <v>1.1261</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4502</v>
+        <v>0.7887</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7484</v>
+        <v>0.3374</v>
       </c>
       <c r="V3" t="n">
         <v>-1.7513</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6642</v>
+        <v>4.2472</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4912</v>
+        <v>3.5145</v>
       </c>
       <c r="F4" t="n">
-        <v>1.173</v>
+        <v>0.7326</v>
       </c>
       <c r="G4" t="n">
         <v>2.5752</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0484</v>
+        <v>0.6314</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2519</v>
+        <v>-0.2286</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3003</v>
+        <v>0.8599</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3435</v>
+        <v>3.6376</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7003</v>
+        <v>1.7889</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6431</v>
+        <v>1.8486</v>
       </c>
       <c r="G5" t="n">
         <v>2.7814</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0189</v>
+        <v>0.313</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0215</v>
+        <v>0.11</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0026</v>
+        <v>0.203</v>
       </c>
       <c r="V5" t="n">
         <v>1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5686</v>
+        <v>1.7009</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9685</v>
+        <v>-0.1298</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5371</v>
+        <v>1.8307</v>
       </c>
       <c r="G6" t="n">
         <v>3.1561</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7144</v>
+        <v>0.4179</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8358</v>
+        <v>0.0029</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1214</v>
+        <v>0.415</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MIRANDA PASCUAL</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1857</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1957</v>
+        <v>-0.8966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0101</v>
+        <v>1.8387</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0618</v>
+        <v>-1.7963</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4903</v>
+        <v>-0.6353</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5715</v>
+        <v>-1.161</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3882</v>
+        <v>-1.2489</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3262</v>
+        <v>0.9122</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7144</v>
+        <v>-2.1611</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6737</v>
+        <v>-0.5474</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8165</v>
+        <v>-1.5475</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1429</v>
+        <v>1.0001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>2.4974</v>
       </c>
       <c r="S7" t="n">
+        <v>0.8215</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.4599</v>
       </c>
-      <c r="T7" t="n">
-        <v>0.1924</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.2675</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>D. MIRANDA PASCUAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2799</v>
+        <v>-0.5952</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1352</v>
+        <v>-0.5172</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.415</v>
+        <v>-0.078</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4018</v>
+        <v>-1.0618</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7014</v>
+        <v>-0.4903</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2996</v>
+        <v>-0.5715</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1569</v>
+        <v>-0.3882</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5992</v>
+        <v>0.3262</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5576</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7551</v>
+        <v>-0.6737</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1022</v>
+        <v>-0.8165</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8572</v>
+        <v>0.1429</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2082</v>
+        <v>0.0504</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0621</v>
+        <v>-0.129</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1462</v>
+        <v>0.1794</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5704</v>
+        <v>-0.6852</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0568</v>
+        <v>-0.2701</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4864</v>
+        <v>-0.415</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7963</v>
+        <v>-0.4018</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6353</v>
+        <v>-0.7014</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.161</v>
+        <v>0.2996</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2489</v>
+        <v>-1.1569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9122</v>
+        <v>-0.5992</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1611</v>
+        <v>-0.5576</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5474</v>
+        <v>0.7551</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5475</v>
+        <v>-0.1022</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0001</v>
+        <v>0.8572</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4974</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6909</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1201</v>
+        <v>0.1462</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4599</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0437</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6595</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0.1305</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7899</v>
+        <v>-0.878</v>
       </c>
       <c r="G10" t="n">
         <v>0.2282</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0718</v>
+        <v>-0.0163</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2675</v>
+        <v>0.1794</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2334</v>
+        <v>-1.0126</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1947</v>
+        <v>-1.9151</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9613</v>
+        <v>0.9026</v>
       </c>
       <c r="G11" t="n">
         <v>0.6820000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2094</v>
+        <v>0.4303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3262</v>
+        <v>-0.0467</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5357</v>
+        <v>0.4769</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3563</v>
+        <v>-2.203</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.9141</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.377</v>
+        <v>-1.2889</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4586</v>
@@ -1390,13 +1390,13 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1246</v>
+        <v>0.0287</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1214</v>
+        <v>-0.0562</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0032</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9813</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.4251</v>
+        <v>16.73</v>
       </c>
       <c r="E13" t="n">
-        <v>7.516699999999998</v>
+        <v>8.821699999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>7.908500000000001</v>
+        <v>7.908499999999998</v>
       </c>
       <c r="G13" t="n">
         <v>14.2465</v>
@@ -1447,7 +1447,7 @@
         <v>15.1678</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7552999999999996</v>
+        <v>-0.7552999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-0.1658999999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-9.4527</v>
       </c>
       <c r="O13" t="n">
-        <v>9.2866</v>
+        <v>9.286599999999998</v>
       </c>
       <c r="P13" t="n">
         <v>1.0405</v>
@@ -1468,13 +1468,13 @@
         <v>13.5275</v>
       </c>
       <c r="S13" t="n">
-        <v>4.224199999999999</v>
+        <v>5.529199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.479</v>
+        <v>1.7838</v>
       </c>
       <c r="U13" t="n">
-        <v>3.745299999999999</v>
+        <v>3.745300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0864</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4394</v>
+        <v>3.2579</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7841</v>
+        <v>2.1055</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6554</v>
+        <v>1.1523</v>
       </c>
       <c r="G14" t="n">
         <v>1.5283</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>0.368</v>
+        <v>0.1864</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1496</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5176</v>
+        <v>1.0146</v>
       </c>
       <c r="V14" t="n">
         <v>1.7513</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9628</v>
+        <v>2.0508</v>
       </c>
       <c r="E15" t="n">
         <v>1.6511</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3117</v>
+        <v>0.3998</v>
       </c>
       <c r="G15" t="n">
         <v>0.6589</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0718</v>
+        <v>0.0163</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0587</v>
+        <v>0.1468</v>
       </c>
       <c r="V15" t="n">
         <v>1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. ARANAZ ALVAREZ</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1937</v>
+        <v>0.9651</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7873</v>
+        <v>1.2787</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9811</v>
+        <v>-0.3137</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2859</v>
+        <v>-2.6976</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2857</v>
+        <v>-0.0239</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0001</v>
+        <v>-2.6738</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3838</v>
+        <v>-0.4766</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3838</v>
+        <v>2.3809</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-2.8575</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9021</v>
+        <v>-2.221</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.098</v>
+        <v>-2.4047</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0001</v>
+        <v>0.1837</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2597</v>
+        <v>-0.0886</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1305</v>
+        <v>-0.3528</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1292</v>
+        <v>0.2643</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.1488</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>H. ARANAZ ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1168</v>
+        <v>0.4286</v>
       </c>
       <c r="E17" t="n">
-        <v>0.743</v>
+        <v>-0.7873</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8597</v>
+        <v>1.2159</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6976</v>
+        <v>1.2859</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0239</v>
+        <v>0.2857</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6738</v>
+        <v>1.0001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4766</v>
+        <v>0.3838</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3809</v>
+        <v>0.3838</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.8575</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.221</v>
+        <v>0.9021</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.4047</v>
+        <v>-0.098</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1837</v>
+        <v>1.0001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1704</v>
+        <v>-0.0248</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.1305</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2818</v>
+        <v>0.1057</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. PIEKUS</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1174</v>
+        <v>0.0311</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0081</v>
+        <v>0.3572</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1254</v>
+        <v>-0.326</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3091</v>
+        <v>-0.7751</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4927</v>
+        <v>0.2536</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8164</v>
+        <v>-1.0287</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4709</v>
+        <v>1.3683</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4709</v>
+        <v>2.0827</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.7144</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.78</v>
+        <v>-2.1434</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9636</v>
+        <v>-1.8291</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8164</v>
+        <v>-0.3143</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5455</v>
+        <v>-0.0481</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7641</v>
+        <v>-0.4305</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2185</v>
+        <v>0.3824</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3538</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8137</v>
+        <v>0.4599</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6393</v>
+        <v>-0.4083</v>
       </c>
       <c r="E19" t="n">
         <v>-0.1305</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5088</v>
+        <v>-0.2779</v>
       </c>
       <c r="G19" t="n">
         <v>-0.347</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2923</v>
+        <v>-0.0613</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1618</v>
+        <v>0.0692</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>P. PIEKUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0253</v>
+        <v>-1.0588</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1786</v>
+        <v>0.7222</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8467</v>
+        <v>-1.781</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7751</v>
+        <v>-1.3091</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2536</v>
+        <v>-0.4927</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0287</v>
+        <v>-0.8164</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3683</v>
+        <v>0.4709</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0827</v>
+        <v>0.4709</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7144</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1434</v>
+        <v>-1.78</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8291</v>
+        <v>-0.9636</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3143</v>
+        <v>-0.8164</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1045</v>
+        <v>0.6041</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9663</v>
+        <v>0.4782</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1383</v>
+        <v>0.1259</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4599</v>
+        <v>0.8137</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7125</v>
+        <v>-1.8158</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4776</v>
+        <v>-0.7873</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7652</v>
+        <v>-1.0285</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.397</v>
+        <v>0.2404</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.401</v>
+        <v>0.4159</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.996</v>
+        <v>-0.1755</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6169</v>
+        <v>0.71</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1881</v>
+        <v>0.71</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4287</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7801</v>
+        <v>-0.4696</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2129</v>
+        <v>-0.294</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4327</v>
+        <v>-0.1755</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6244</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>0.079</v>
+        <v>-0.3882</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4476</v>
+        <v>-0.4567</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5266</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.9813</v>
+        <v>-1.0437</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3538</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8921</v>
+        <v>-2.1719</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7873</v>
+        <v>-2.5848</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1048</v>
+        <v>0.4129</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2404</v>
+        <v>-4.397</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4159</v>
+        <v>-3.401</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1755</v>
+        <v>-0.996</v>
       </c>
       <c r="J22" t="n">
-        <v>0.71</v>
+        <v>-2.6169</v>
       </c>
       <c r="K22" t="n">
-        <v>0.71</v>
+        <v>-1.1881</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.4287</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4696</v>
+        <v>-1.7801</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.294</v>
+        <v>-2.2129</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1755</v>
+        <v>0.4327</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4645</v>
+        <v>-0.3805</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4567</v>
+        <v>-0.5548</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0078</v>
+        <v>0.1743</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0437</v>
+        <v>1.9813</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0437</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9998</v>
+        <v>-2.9308</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8539</v>
+        <v>-1.9611</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1459</v>
+        <v>-0.9697</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8962</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4574</v>
+        <v>-0.3884</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0562</v>
+        <v>-0.1633</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4012</v>
+        <v>-0.225</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9847</v>
+        <v>-3.695</v>
       </c>
       <c r="E24" t="n">
         <v>-1.1212</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8635</v>
+        <v>-2.5738</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9056</v>
@@ -2326,13 +2326,13 @@
         <v>0.6244</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1385</v>
+        <v>-0.8488</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5219</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6165</v>
+        <v>-0.3268</v>
       </c>
       <c r="V24" t="n">
         <v>-2.565</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.533300000000001</v>
+        <v>-7.9348</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.7581</v>
+        <v>-6.6509</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7752</v>
+        <v>-1.2839</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6323</v>
@@ -2404,13 +2404,13 @@
         <v>2.2893</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2579</v>
+        <v>-0.6595</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.631</v>
+        <v>-0.5238</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6269</v>
+        <v>-0.1357</v>
       </c>
       <c r="V25" t="n">
         <v>0.23</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.4253</v>
+        <v>-13.2819</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.908199999999999</v>
+        <v>-7.9084</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.5166</v>
+        <v>-5.3736</v>
       </c>
       <c r="G26" t="n">
         <v>-14.2464</v>
@@ -2461,7 +2461,7 @@
         <v>9.4528</v>
       </c>
       <c r="L26" t="n">
-        <v>-9.286799999999999</v>
+        <v>-9.286800000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-14.4124</v>
@@ -2482,13 +2482,13 @@
         <v>12.4871</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.224500000000001</v>
+        <v>-2.0814</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7453</v>
+        <v>-3.7452</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4791000000000001</v>
+        <v>1.6642</v>
       </c>
       <c r="V26" t="n">
         <v>4.086399999999999</v>
@@ -2497,7 +2497,7 @@
         <v>9.198700000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.1124</v>
+        <v>-5.112399999999999</v>
       </c>
     </row>
   </sheetData>
